--- a/sheets/대금율보/검수/꼭두각시.xlsx
+++ b/sheets/대금율보/검수/꼭두각시.xlsx
@@ -5521,15 +5521,13 @@
         <is>
           <t xml:space="preserve">南
 林
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G6" s="24"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I6" s="24"/>
@@ -5753,8 +5751,7 @@
         <is>
           <t xml:space="preserve">㴌
 汰
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="E10" s="24"/>
@@ -5774,15 +5771,13 @@
       <c r="I10" s="24"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ʒ
-‹</t>
+          <t xml:space="preserve">淋ʒ</t>
         </is>
       </c>
       <c r="K10" s="24"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ʒ
-‹</t>
+          <t xml:space="preserve">淋ʒ</t>
         </is>
       </c>
       <c r="M10" s="24"/>
@@ -6014,8 +6009,7 @@
         <is>
           <t xml:space="preserve">南
 林
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G14" s="24"/>
@@ -6023,8 +6017,7 @@
         <is>
           <t xml:space="preserve">南
 林
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -6032,8 +6025,7 @@
         <is>
           <t xml:space="preserve">㴌
 汰
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="K14" s="24"/>
@@ -6269,15 +6261,13 @@
       <c r="I18" s="24"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K18" s="24"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ʒ
-‹</t>
+          <t xml:space="preserve">淋ʒ</t>
         </is>
       </c>
       <c r="M18" s="24"/>

--- a/sheets/대금율보/검수/꼭두각시.xlsx
+++ b/sheets/대금율보/검수/꼭두각시.xlsx
@@ -5278,28 +5278,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11.63" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="11.63" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="11.63" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="11.63" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.63" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="11.63" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="11.63" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="11.63" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="Q5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="Q6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="Q8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="Q9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="Q10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="Q11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="Q12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="Q14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="Q15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="Q16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="Q17" s="26"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6290,6 +6290,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>